--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0033.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0033.xlsx
@@ -17734,7 +17734,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Cato và Aeolus đang bị kẹt ở đằng kia, đội của ta không thể liên lạc với họ được. Chúng ta... Ta...!</t>
+          <t>Cato và Aeolus đang bị kẹt ở đằng kia, đội của tao không thể liên lạc với họ được. Chúng ta... Tao...!</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Ta cứ nghĩ cậu phải tự làm việc đó chứ.</t>
+          <t>Tao cứ nghĩ cậu phải tự làm việc đó chứ.</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Nghe không giống Hiệp Hội Tiên Phong mà ta biết.</t>
+          <t>Nghe không giống Hiệp Hội Tiên Phong mà tao biết.</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Này! Ít nhất cũng tin ta một chút chứ. Ta nói thật là ta làm cho Hiệp Hội Tiên Phong đấy. Ta chỉ kiêm luôn việc tổ chức mấy buổi tập luyện thôi.</t>
+          <t>Này! Ít nhất cũng tin tao một chút chứ. Tao nói thật là tao làm cho Hiệp Hội Tiên Phong đấy. Tao chỉ kiêm luôn việc tổ chức mấy buổi tập luyện thôi.</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Dù một ngày nào đó không còn làm nghề bán hàng nữa, ta vẫn sẽ chu du khắp Solaris và ghi lại từng khoảnh khắc nghẹt thở như thế này!</t>
+          <t>Dù một ngày nào đó không còn làm nghề bán hàng nữa, tao vẫn sẽ chu du khắp Solaris và ghi lại từng khoảnh khắc nghẹt thở như thế này!</t>
         </is>
       </c>
     </row>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Ừ, đây là phần thưởng ta chuẩn bị cho cậu, cảm ơn vì những đóng góp của cậu cho thế giới thể thao mạo hiểm.</t>
+          <t>Ừ, đây là phần thưởng tao chuẩn bị cho cậu, cảm ơn vì những đóng góp của cậu cho thế giới thể thao mạo hiểm.</t>
         </is>
       </c>
     </row>
